--- a/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP264"/>
+  <dimension ref="A1:BP265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.23</v>
@@ -7236,7 +7236,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR31" t="n">
         <v>2.05</v>
@@ -7672,7 +7672,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR33" t="n">
         <v>1.38</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.38</v>
@@ -12465,7 +12465,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.86</v>
@@ -13558,7 +13558,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR60" t="n">
         <v>2.05</v>
@@ -17264,7 +17264,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR77" t="n">
         <v>1.18</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.85</v>
@@ -22278,7 +22278,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR100" t="n">
         <v>1.06</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.15</v>
@@ -24894,7 +24894,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR112" t="n">
         <v>0.99</v>
@@ -26417,7 +26417,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ119" t="n">
         <v>2.23</v>
@@ -29469,7 +29469,7 @@
         <v>1.5</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.69</v>
@@ -30998,7 +30998,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR140" t="n">
         <v>1.44</v>
@@ -36884,7 +36884,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR167" t="n">
         <v>1.6</v>
@@ -39061,7 +39061,7 @@
         <v>1.5</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.46</v>
@@ -41244,7 +41244,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR187" t="n">
         <v>1.63</v>
@@ -42985,7 +42985,7 @@
         <v>1.8</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.67</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.85</v>
@@ -45386,7 +45386,7 @@
         <v>1</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR206" t="n">
         <v>1.17</v>
@@ -46691,7 +46691,7 @@
         <v>0.7</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ212" t="n">
         <v>0.62</v>
@@ -48874,7 +48874,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ222" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR222" t="n">
         <v>1.38</v>
@@ -53667,7 +53667,7 @@
         <v>1.67</v>
       </c>
       <c r="AP244" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.54</v>
@@ -54106,7 +54106,7 @@
         <v>1</v>
       </c>
       <c r="AQ246" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR246" t="n">
         <v>1.03</v>
@@ -58106,6 +58106,224 @@
       </c>
       <c r="BP264" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>8238586</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>46081.69791666666</v>
+      </c>
+      <c r="F265" t="n">
+        <v>27</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" t="n">
+        <v>2</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>2</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>['31', '70']</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S265" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V265" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X265" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP265"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.67</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.57</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.38</v>
@@ -3312,7 +3312,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.69</v>
@@ -4399,10 +4399,10 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR19" t="n">
         <v>0.7</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -6143,7 +6143,7 @@
         <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.23</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR28" t="n">
         <v>0.77</v>
@@ -6800,7 +6800,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR29" t="n">
         <v>2.48</v>
@@ -7890,7 +7890,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>2.22</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR35" t="n">
         <v>1.48</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.46</v>
@@ -8759,10 +8759,10 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR38" t="n">
         <v>1.01</v>
@@ -9852,7 +9852,7 @@
         <v>2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -10285,7 +10285,7 @@
         <v>3</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.23</v>
@@ -10503,10 +10503,10 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR46" t="n">
         <v>1.01</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.57</v>
@@ -10942,7 +10942,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR48" t="n">
         <v>1.12</v>
@@ -11596,7 +11596,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR51" t="n">
         <v>0.83</v>
@@ -12901,7 +12901,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57" t="n">
         <v>1</v>
@@ -13776,7 +13776,7 @@
         <v>2</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR61" t="n">
         <v>2.23</v>
@@ -14209,7 +14209,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.57</v>
@@ -14427,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.67</v>
@@ -14645,7 +14645,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ65" t="n">
         <v>2.54</v>
@@ -14866,7 +14866,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR66" t="n">
         <v>1.63</v>
@@ -15084,7 +15084,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR67" t="n">
         <v>1.18</v>
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR69" t="n">
         <v>2.03</v>
@@ -15738,7 +15738,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR70" t="n">
         <v>1.5</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.23</v>
@@ -16607,7 +16607,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.85</v>
@@ -17043,10 +17043,10 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR76" t="n">
         <v>1.01</v>
@@ -17261,7 +17261,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.85</v>
@@ -17697,7 +17697,7 @@
         <v>3</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.69</v>
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR80" t="n">
         <v>1.22</v>
@@ -18136,7 +18136,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR81" t="n">
         <v>1.43</v>
@@ -18572,7 +18572,7 @@
         <v>2</v>
       </c>
       <c r="AQ83" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR83" t="n">
         <v>2</v>
@@ -19005,7 +19005,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.46</v>
@@ -19662,7 +19662,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR88" t="n">
         <v>2.24</v>
@@ -20313,10 +20313,10 @@
         <v>1</v>
       </c>
       <c r="AP91" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR91" t="n">
         <v>0.95</v>
@@ -20531,10 +20531,10 @@
         <v>1.5</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR92" t="n">
         <v>1.5</v>
@@ -20967,10 +20967,10 @@
         <v>1</v>
       </c>
       <c r="AP94" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR94" t="n">
         <v>1.05</v>
@@ -21403,7 +21403,7 @@
         <v>0.5</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.62</v>
@@ -21842,7 +21842,7 @@
         <v>1</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR98" t="n">
         <v>1.08</v>
@@ -22275,7 +22275,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.85</v>
@@ -22711,7 +22711,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.86</v>
@@ -23586,7 +23586,7 @@
         <v>1</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR106" t="n">
         <v>1</v>
@@ -24240,7 +24240,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR109" t="n">
         <v>1.43</v>
@@ -24455,7 +24455,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.23</v>
@@ -24676,7 +24676,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR111" t="n">
         <v>2.29</v>
@@ -25109,10 +25109,10 @@
         <v>1.33</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR113" t="n">
         <v>1.46</v>
@@ -25330,7 +25330,7 @@
         <v>1</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR114" t="n">
         <v>1.42</v>
@@ -25548,7 +25548,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR115" t="n">
         <v>1.65</v>
@@ -25981,7 +25981,7 @@
         <v>2.4</v>
       </c>
       <c r="AP117" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.69</v>
@@ -26420,7 +26420,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR119" t="n">
         <v>2.07</v>
@@ -26635,7 +26635,7 @@
         <v>1.2</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.69</v>
@@ -26853,7 +26853,7 @@
         <v>0.6</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.62</v>
@@ -27946,7 +27946,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR126" t="n">
         <v>1.71</v>
@@ -28379,7 +28379,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ128" t="n">
         <v>2.54</v>
@@ -28600,7 +28600,7 @@
         <v>2</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR129" t="n">
         <v>1.86</v>
@@ -28815,7 +28815,7 @@
         <v>1.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.67</v>
@@ -29251,10 +29251,10 @@
         <v>0.57</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR132" t="n">
         <v>1.34</v>
@@ -29690,7 +29690,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR134" t="n">
         <v>1.49</v>
@@ -29905,7 +29905,7 @@
         <v>1.17</v>
       </c>
       <c r="AP135" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.85</v>
@@ -30344,7 +30344,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR137" t="n">
         <v>1.47</v>
@@ -30562,7 +30562,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR138" t="n">
         <v>1.6</v>
@@ -30777,7 +30777,7 @@
         <v>0.83</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.46</v>
@@ -30995,7 +30995,7 @@
         <v>0.83</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.85</v>
@@ -31213,10 +31213,10 @@
         <v>2</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR141" t="n">
         <v>1.28</v>
@@ -31649,7 +31649,7 @@
         <v>1.57</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.86</v>
@@ -31870,7 +31870,7 @@
         <v>1</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR144" t="n">
         <v>1.14</v>
@@ -32739,7 +32739,7 @@
         <v>1.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.67</v>
@@ -33178,7 +33178,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR150" t="n">
         <v>1.79</v>
@@ -33393,7 +33393,7 @@
         <v>1.29</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.69</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
         <v>1</v>
@@ -34704,7 +34704,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR157" t="n">
         <v>1.35</v>
@@ -34922,7 +34922,7 @@
         <v>1</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR158" t="n">
         <v>1.24</v>
@@ -35355,7 +35355,7 @@
         <v>0.75</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ160" t="n">
         <v>1</v>
@@ -35573,10 +35573,10 @@
         <v>1</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR161" t="n">
         <v>1.57</v>
@@ -35791,10 +35791,10 @@
         <v>1.38</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR162" t="n">
         <v>1.12</v>
@@ -36227,7 +36227,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.67</v>
@@ -36881,7 +36881,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.85</v>
@@ -37102,7 +37102,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR168" t="n">
         <v>1.19</v>
@@ -37753,7 +37753,7 @@
         <v>1.14</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.46</v>
@@ -39064,7 +39064,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR177" t="n">
         <v>2.01</v>
@@ -39279,7 +39279,7 @@
         <v>1.33</v>
       </c>
       <c r="AP178" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.69</v>
@@ -39715,10 +39715,10 @@
         <v>1.56</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR180" t="n">
         <v>1.29</v>
@@ -40154,7 +40154,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR182" t="n">
         <v>1.72</v>
@@ -40372,7 +40372,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR183" t="n">
         <v>1.35</v>
@@ -40805,7 +40805,7 @@
         <v>1.11</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.23</v>
@@ -41023,7 +41023,7 @@
         <v>1</v>
       </c>
       <c r="AP186" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ186" t="n">
         <v>1</v>
@@ -41462,7 +41462,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR188" t="n">
         <v>1.67</v>
@@ -41677,7 +41677,7 @@
         <v>0.67</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.62</v>
@@ -41895,7 +41895,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.38</v>
@@ -42552,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="AQ193" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR193" t="n">
         <v>1.65</v>
@@ -42770,7 +42770,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR194" t="n">
         <v>1.43</v>
@@ -44078,7 +44078,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR200" t="n">
         <v>1.39</v>
@@ -44296,7 +44296,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ201" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR201" t="n">
         <v>1.62</v>
@@ -44511,10 +44511,10 @@
         <v>1.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR202" t="n">
         <v>1.11</v>
@@ -44729,7 +44729,7 @@
         <v>2.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ203" t="n">
         <v>2.54</v>
@@ -45168,7 +45168,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR205" t="n">
         <v>1.14</v>
@@ -45604,7 +45604,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR207" t="n">
         <v>1.67</v>
@@ -45819,7 +45819,7 @@
         <v>1.8</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.69</v>
@@ -46255,7 +46255,7 @@
         <v>0.7</v>
       </c>
       <c r="AP210" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.57</v>
@@ -47348,7 +47348,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR215" t="n">
         <v>1.18</v>
@@ -47563,7 +47563,7 @@
         <v>1.09</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.86</v>
@@ -47784,7 +47784,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR217" t="n">
         <v>1.31</v>
@@ -48435,10 +48435,10 @@
         <v>2.2</v>
       </c>
       <c r="AP220" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR220" t="n">
         <v>1.75</v>
@@ -49089,7 +49089,7 @@
         <v>1.09</v>
       </c>
       <c r="AP223" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.38</v>
@@ -49310,7 +49310,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ224" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR224" t="n">
         <v>1.56</v>
@@ -49743,7 +49743,7 @@
         <v>0.8</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.85</v>
@@ -49964,7 +49964,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR227" t="n">
         <v>1.69</v>
@@ -50179,7 +50179,7 @@
         <v>2.4</v>
       </c>
       <c r="AP228" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ228" t="n">
         <v>2.54</v>
@@ -50400,7 +50400,7 @@
         <v>1</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR229" t="n">
         <v>1.18</v>
@@ -50615,7 +50615,7 @@
         <v>1.91</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ230" t="n">
         <v>1.69</v>
@@ -50836,7 +50836,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ231" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR231" t="n">
         <v>1.68</v>
@@ -52141,7 +52141,7 @@
         <v>2.45</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ237" t="n">
         <v>2.54</v>
@@ -52362,7 +52362,7 @@
         <v>2</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR238" t="n">
         <v>2.13</v>
@@ -52795,7 +52795,7 @@
         <v>1.08</v>
       </c>
       <c r="AP240" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ240" t="n">
         <v>1</v>
@@ -53013,10 +53013,10 @@
         <v>2.17</v>
       </c>
       <c r="AP241" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AQ241" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AR241" t="n">
         <v>1.21</v>
@@ -53234,7 +53234,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ242" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR242" t="n">
         <v>1.8</v>
@@ -53452,7 +53452,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ243" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR243" t="n">
         <v>1.39</v>
@@ -53670,7 +53670,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR244" t="n">
         <v>2.16</v>
@@ -53885,7 +53885,7 @@
         <v>1.25</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.38</v>
@@ -54103,7 +54103,7 @@
         <v>0.91</v>
       </c>
       <c r="AP246" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ246" t="n">
         <v>0.85</v>
@@ -54539,10 +54539,10 @@
         <v>1.33</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR248" t="n">
         <v>1.42</v>
@@ -55411,7 +55411,7 @@
         <v>0.62</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ252" t="n">
         <v>0.57</v>
@@ -56068,7 +56068,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR255" t="n">
         <v>1.09</v>
@@ -56937,7 +56937,7 @@
         <v>0.92</v>
       </c>
       <c r="AP259" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ259" t="n">
         <v>0.86</v>
@@ -58324,6 +58324,1314 @@
       </c>
       <c r="BP265" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>8238755</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>46082.35416666666</v>
+      </c>
+      <c r="F266" t="n">
+        <v>27</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>2</v>
+      </c>
+      <c r="N266" t="n">
+        <v>2</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['89', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>7</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S266" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X266" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>8238783</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F267" t="n">
+        <v>27</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>2</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="N267" t="n">
+        <v>3</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>['23', '69']</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>4</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S267" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U267" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V267" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X267" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>8238489</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>46082.58333333334</v>
+      </c>
+      <c r="F268" t="n">
+        <v>27</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1</v>
+      </c>
+      <c r="L268" t="n">
+        <v>2</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>2</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>['21', '53']</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2</v>
+      </c>
+      <c r="S268" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U268" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X268" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>8238460</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>46082.69791666666</v>
+      </c>
+      <c r="F269" t="n">
+        <v>27</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1</v>
+      </c>
+      <c r="L269" t="n">
+        <v>3</v>
+      </c>
+      <c r="M269" t="n">
+        <v>3</v>
+      </c>
+      <c r="N269" t="n">
+        <v>6</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>['39', '54', '65']</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>['47', '78', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S269" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U269" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V269" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X269" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>8238488</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>46083.60416666666</v>
+      </c>
+      <c r="F270" t="n">
+        <v>27</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S270" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V270" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X270" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BI270" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BM270" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BN270" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO270" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP270" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>8238587</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>46083.69791666666</v>
+      </c>
+      <c r="F271" t="n">
+        <v>27</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" t="n">
+        <v>3</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>3</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>['10', '63', '90+4']</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S271" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U271" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V271" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X271" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO271" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BP271" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.79</v>
@@ -2876,7 +2876,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
         <v>1</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.46</v>
@@ -5928,7 +5928,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR25" t="n">
         <v>1.43</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR39" t="n">
         <v>1.75</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.62</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44" t="n">
         <v>2.54</v>
@@ -11378,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR50" t="n">
         <v>0.97</v>
@@ -12250,7 +12250,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR54" t="n">
         <v>1.56</v>
@@ -12686,7 +12686,7 @@
         <v>2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR56" t="n">
         <v>2.23</v>
@@ -13555,7 +13555,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.85</v>
@@ -15081,7 +15081,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.57</v>
@@ -16392,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR73" t="n">
         <v>1.09</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ75" t="n">
         <v>2.54</v>
@@ -19444,7 +19444,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR87" t="n">
         <v>1.81</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.38</v>
@@ -20749,10 +20749,10 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR93" t="n">
         <v>1.65</v>
@@ -23368,7 +23368,7 @@
         <v>2</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR105" t="n">
         <v>2.17</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.85</v>
@@ -25545,7 +25545,7 @@
         <v>1.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.31</v>
@@ -26638,7 +26638,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR120" t="n">
         <v>1.33</v>
@@ -28164,7 +28164,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR127" t="n">
         <v>1.17</v>
@@ -29472,7 +29472,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR133" t="n">
         <v>2.1</v>
@@ -30123,7 +30123,7 @@
         <v>2.5</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.69</v>
@@ -30559,7 +30559,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.5</v>
@@ -33396,7 +33396,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR151" t="n">
         <v>1.6</v>
@@ -34047,7 +34047,7 @@
         <v>0.57</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.62</v>
@@ -34268,7 +34268,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR155" t="n">
         <v>1.35</v>
@@ -35140,7 +35140,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR159" t="n">
         <v>1.23</v>
@@ -37099,7 +37099,7 @@
         <v>2.14</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ168" t="n">
         <v>2.29</v>
@@ -38846,7 +38846,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR176" t="n">
         <v>1.49</v>
@@ -39282,7 +39282,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR178" t="n">
         <v>1.1</v>
@@ -39933,7 +39933,7 @@
         <v>0.67</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.57</v>
@@ -42116,7 +42116,7 @@
         <v>2</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR191" t="n">
         <v>1.75</v>
@@ -43639,7 +43639,7 @@
         <v>1.33</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.46</v>
@@ -44947,7 +44947,7 @@
         <v>1.2</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.38</v>
@@ -45165,7 +45165,7 @@
         <v>1.7</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.5</v>
@@ -46476,7 +46476,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR211" t="n">
         <v>1.42</v>
@@ -46912,7 +46912,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR213" t="n">
         <v>1.68</v>
@@ -49307,7 +49307,7 @@
         <v>0.73</v>
       </c>
       <c r="AP224" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ224" t="n">
         <v>0.79</v>
@@ -49525,7 +49525,7 @@
         <v>0.73</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.57</v>
@@ -51490,7 +51490,7 @@
         <v>1</v>
       </c>
       <c r="AQ234" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR234" t="n">
         <v>1.69</v>
@@ -54757,7 +54757,7 @@
         <v>1.75</v>
       </c>
       <c r="AP249" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ249" t="n">
         <v>1.69</v>
@@ -54975,7 +54975,7 @@
         <v>0.73</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.85</v>
@@ -55196,7 +55196,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR251" t="n">
         <v>1.84</v>
@@ -55632,7 +55632,7 @@
         <v>2</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR253" t="n">
         <v>2.22</v>
@@ -56065,7 +56065,7 @@
         <v>1.17</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ255" t="n">
         <v>1.07</v>
@@ -56286,7 +56286,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ256" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR256" t="n">
         <v>1.31</v>
@@ -59632,6 +59632,442 @@
       </c>
       <c r="BP271" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>8238588</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>46087.69791666666</v>
+      </c>
+      <c r="F272" t="n">
+        <v>28</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" t="n">
+        <v>2</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1</v>
+      </c>
+      <c r="N272" t="n">
+        <v>3</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>['7', '68']</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R272" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S272" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U272" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V272" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W272" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X272" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA272" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB272" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI272" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM272" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN272" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO272" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP272" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>8238728</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>46088.45833333334</v>
+      </c>
+      <c r="F273" t="n">
+        <v>28</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="n">
+        <v>2</v>
+      </c>
+      <c r="N273" t="n">
+        <v>3</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>['14', '76']</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="R273" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S273" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U273" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V273" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W273" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X273" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI273" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ273" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK273" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BL273" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BM273" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN273" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO273" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP273" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Italy Serie A_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP273"/>
+  <dimension ref="A1:BP275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.46</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR20" t="n">
         <v>2.18</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ23" t="n">
         <v>2.54</v>
@@ -6146,7 +6146,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR26" t="n">
         <v>0.82</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.85</v>
@@ -9416,7 +9416,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR41" t="n">
         <v>2.21</v>
@@ -9849,7 +9849,7 @@
         <v>2</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.31</v>
@@ -10288,7 +10288,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR45" t="n">
         <v>0.95</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.79</v>
@@ -13122,7 +13122,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR58" t="n">
         <v>1.51</v>
@@ -13773,7 +13773,7 @@
         <v>3</v>
       </c>
       <c r="AP61" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.29</v>
@@ -15517,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.07</v>
@@ -15956,7 +15956,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR71" t="n">
         <v>0.92</v>
@@ -16174,7 +16174,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -18569,7 +18569,7 @@
         <v>2.33</v>
       </c>
       <c r="AP83" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ83" t="n">
         <v>2.29</v>
@@ -19223,10 +19223,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR86" t="n">
         <v>2.02</v>
@@ -21406,7 +21406,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR96" t="n">
         <v>1.29</v>
@@ -23365,7 +23365,7 @@
         <v>1</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.93</v>
@@ -23801,7 +23801,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.38</v>
@@ -24458,7 +24458,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR110" t="n">
         <v>1.74</v>
@@ -26856,7 +26856,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR121" t="n">
         <v>1.13</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR123" t="n">
         <v>1.07</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ125" t="n">
         <v>1</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.79</v>
@@ -31434,7 +31434,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR142" t="n">
         <v>1.14</v>
@@ -32085,7 +32085,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ145" t="n">
         <v>1</v>
@@ -33829,7 +33829,7 @@
         <v>2.14</v>
       </c>
       <c r="AP153" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.69</v>
@@ -34050,7 +34050,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR154" t="n">
         <v>1.15</v>
@@ -34486,7 +34486,7 @@
         <v>1</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR156" t="n">
         <v>1.47</v>
@@ -36663,7 +36663,7 @@
         <v>2.14</v>
       </c>
       <c r="AP166" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ166" t="n">
         <v>2.54</v>
@@ -37320,7 +37320,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR169" t="n">
         <v>1.68</v>
@@ -37538,7 +37538,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR170" t="n">
         <v>1.29</v>
@@ -37971,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="AP172" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.85</v>
@@ -38189,7 +38189,7 @@
         <v>1.88</v>
       </c>
       <c r="AP173" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.69</v>
@@ -40808,7 +40808,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR185" t="n">
         <v>1.44</v>
@@ -41680,7 +41680,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR189" t="n">
         <v>1.58</v>
@@ -42113,7 +42113,7 @@
         <v>1.33</v>
       </c>
       <c r="AP191" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.93</v>
@@ -43421,7 +43421,7 @@
         <v>1.2</v>
       </c>
       <c r="AP197" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.86</v>
@@ -46694,7 +46694,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR212" t="n">
         <v>2.01</v>
@@ -47999,7 +47999,7 @@
         <v>1.3</v>
       </c>
       <c r="AP218" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.46</v>
@@ -48217,7 +48217,7 @@
         <v>1.73</v>
       </c>
       <c r="AP219" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ219" t="n">
         <v>1.67</v>
@@ -48656,7 +48656,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR221" t="n">
         <v>1.4</v>
@@ -51054,7 +51054,7 @@
         <v>0.54</v>
       </c>
       <c r="AQ232" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR232" t="n">
         <v>1.37</v>
@@ -51926,7 +51926,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR236" t="n">
         <v>1.2</v>
@@ -52359,7 +52359,7 @@
         <v>1.18</v>
       </c>
       <c r="AP238" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.07</v>
@@ -52577,7 +52577,7 @@
         <v>1</v>
       </c>
       <c r="AP239" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ239" t="n">
         <v>0.86</v>
@@ -55629,7 +55629,7 @@
         <v>1.58</v>
       </c>
       <c r="AP253" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.79</v>
@@ -56501,7 +56501,7 @@
         <v>1.69</v>
       </c>
       <c r="AP257" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ257" t="n">
         <v>1.67</v>
@@ -57158,7 +57158,7 @@
         <v>1</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR260" t="n">
         <v>1.72</v>
@@ -57376,7 +57376,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR261" t="n">
         <v>1.65</v>
@@ -60068,6 +60068,442 @@
       </c>
       <c r="BP273" t="n">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>8238758</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>46088.58333333334</v>
+      </c>
+      <c r="F274" t="n">
+        <v>28</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" t="n">
+        <v>2</v>
+      </c>
+      <c r="M274" t="n">
+        <v>2</v>
+      </c>
+      <c r="N274" t="n">
+        <v>4</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>['75', '79']</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>['39', '55']</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R274" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S274" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U274" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V274" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X274" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO274" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BP274" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>8238784</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>46088.69791666666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>28</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
+        <v>4</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="n">
+        <v>4</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>['54', '65', '75', '90+3']</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="S275" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U275" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V275" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X275" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU275" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY275" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA275" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB275" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BI275" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM275" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN275" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO275" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP275" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
